--- a/medical_consent_forms/049_phq_9_rating_scale--medical_consent_forms.xlsx
+++ b/medical_consent_forms/049_phq_9_rating_scale--medical_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Questions</t>
+          <t>Questions9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -985,29 +985,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>some_or_most_of_the_time</t>
+          <t>most_or_all_of_the_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Some or most of the time</t>
+          <t>Most or all of the time</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>questions3_choices</t>
+          <t>questions4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>most_or_all_of_the_time</t>
+          <t>almost_never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Most or all of the time</t>
+          <t>Almost never</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>almost_never</t>
+          <t>some_or_most_of_the_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Almost never</t>
+          <t>Some or most of the time</t>
         </is>
       </c>
     </row>
@@ -1036,138 +1036,138 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>some_or_most_of_the_time</t>
+          <t>most_or_all_of_the_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Some or most of the time</t>
+          <t>Most or all of the time</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>questions4_choices</t>
+          <t>questions5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>most_or_all_of_the_time</t>
+          <t>none_or_almost_never</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Most or all of the time</t>
+          <t>None or almost never</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>questions4_choices</t>
+          <t>questions5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>most_or_all_of_the_time</t>
+          <t>some_or_most_of_the_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Most or all of the time</t>
+          <t>Some or most of the time</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>questions5_choices</t>
+          <t>questions6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>none_or_almost_never</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None or almost never</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>questions5_choices</t>
+          <t>questions6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>some_or_most_of_the_time</t>
+          <t>most_or_all_of_the_time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Some or most of the time</t>
+          <t>Most or all of the time</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>questions6_choices</t>
+          <t>questions7_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>almost_always</t>
+          <t>most_or_all_of_the_time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Almost always</t>
+          <t>Most or all of the time</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>questions6_choices</t>
+          <t>questions7_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>most_or_all_of_the_time</t>
+          <t>some_or_most_of_the_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Most or all of the time</t>
+          <t>Some or most of the time</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>questions7_choices</t>
+          <t>questions8_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>most_or_all_of_the_time</t>
+          <t>none_or_almost_never</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Most or all of the time</t>
+          <t>None or almost never</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>questions7_choices</t>
+          <t>questions8_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1184,24 +1184,24 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>questions7_choices</t>
+          <t>questions9_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>some_or_most_of_the_time</t>
+          <t>none_or_almost_never</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Some or most of the time</t>
+          <t>None or almost never</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>questions7_choices</t>
+          <t>questions9_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1210,74 +1210,6 @@
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>Some or most of the time</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>questions8_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>none_or_almost_never</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None or almost never</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>questions8_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>some_or_most_of_the_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Some or most of the time</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>questions9_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>none_or_almost_never</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None or almost never</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>questions9_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>some_or_most_of_the_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Some or most of the time</t>
         </is>
